--- a/example/GRAFS_project_example_N.xlsx
+++ b/example/GRAFS_project_example_N.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148CCE2C-F59C-4D88-9908-DFFD3B21270C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A50B46A-7AE4-439F-B399-B5800018DEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
   </bookViews>
   <sheets>
     <sheet name="crops" sheetId="1" r:id="rId1"/>
     <sheet name="livestock" sheetId="2" r:id="rId2"/>
     <sheet name="pop" sheetId="18" r:id="rId3"/>
-    <sheet name="excretion" sheetId="20" r:id="rId4"/>
-    <sheet name="prod" sheetId="12" r:id="rId5"/>
-    <sheet name="global" sheetId="19" r:id="rId6"/>
+    <sheet name="energy" sheetId="21" r:id="rId4"/>
+    <sheet name="excretion" sheetId="20" r:id="rId5"/>
+    <sheet name="prod" sheetId="12" r:id="rId6"/>
+    <sheet name="global" sheetId="19" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="93">
   <si>
     <t>Culture</t>
   </si>
@@ -272,15 +273,6 @@
     <t>forage</t>
   </si>
   <si>
-    <t>Methanizer Energy Production (GWh)</t>
-  </si>
-  <si>
-    <t>Weight methanizer production</t>
-  </si>
-  <si>
-    <t>Weight methanizer inputs</t>
-  </si>
-  <si>
     <t>Green waste methanization power (MWh/ktN)</t>
   </si>
   <si>
@@ -300,13 +292,43 @@
   </si>
   <si>
     <t>Weight import</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>b_2023_fr</t>
+  </si>
+  <si>
+    <t>p_2023_fr</t>
+  </si>
+  <si>
+    <t>fr_2023_fr</t>
+  </si>
+  <si>
+    <t>Facility</t>
+  </si>
+  <si>
+    <t>Methanizer</t>
+  </si>
+  <si>
+    <t>Methanizer_diet</t>
+  </si>
+  <si>
+    <t>Energy Production (GWh)</t>
+  </si>
+  <si>
+    <t>Weight inputs</t>
+  </si>
+  <si>
+    <t>Weight production</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +360,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -380,7 +410,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -392,6 +422,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,13 +783,13 @@
         <v>52</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.35">
@@ -1072,14 +1103,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12223D9-0A39-4CC4-B45B-34CE66BF62BA}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="27.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1089,8 +1120,11 @@
       <c r="C1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1100,8 +1134,11 @@
       <c r="C2">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1110,6 +1147,9 @@
       </c>
       <c r="C3">
         <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1120,17 +1160,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE2E00F-78C5-47A0-A96B-9CB3B1AB6545}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1139,6 +1185,56 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CFCB2E5-50C4-494B-B397-F4A184BDF7BD}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CEBB00-B56F-4BED-97E3-E735E21789EF}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1172,7 +1268,7 @@
         <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
         <v>31</v>
@@ -1288,7 +1384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9008F097-1A19-4A13-A439-D292DC31E615}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1326,10 +1422,10 @@
         <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1653,9 +1749,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986D1BE3-7A15-4223-93AE-9AB753B07534}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.81640625" customWidth="1"/>
@@ -1707,38 +1803,14 @@
         <v>76</v>
       </c>
       <c r="B6">
-        <v>1000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10">
         <v>0</v>
       </c>
     </row>

--- a/example/GRAFS_project_example_N.xlsx
+++ b/example/GRAFS_project_example_N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A50B46A-7AE4-439F-B399-B5800018DEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938FBD28-A109-40DC-B05B-B9058FE0C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
   </bookViews>
   <sheets>
     <sheet name="crops" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
   <si>
     <t>Culture</t>
   </si>
@@ -285,12 +285,6 @@
     <t>Spreading Rate (%)</t>
   </si>
   <si>
-    <t>Seed input (kt seeds/kt Ymax)</t>
-  </si>
-  <si>
-    <t>Methanization power (MWh/tFW)</t>
-  </si>
-  <si>
     <t>Weight import</t>
   </si>
   <si>
@@ -318,10 +312,28 @@
     <t>Energy Production (GWh)</t>
   </si>
   <si>
-    <t>Weight inputs</t>
-  </si>
-  <si>
-    <t>Weight production</t>
+    <t>Weight energy production</t>
+  </si>
+  <si>
+    <t>Weight energy inputs</t>
+  </si>
+  <si>
+    <t>Energy Production (MWh/tFW)</t>
+  </si>
+  <si>
+    <t>Bio_diet</t>
+  </si>
+  <si>
+    <t>Bioraffinery</t>
+  </si>
+  <si>
+    <t>Seed input (ktN/ktN)</t>
+  </si>
+  <si>
+    <t>Total Synthetic Fertilizer Use on crops (ktN)</t>
+  </si>
+  <si>
+    <t>Total Synthetic Fertilizer Use on grasslands (ktN)</t>
   </si>
 </sst>
 </file>
@@ -375,12 +387,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -410,7 +428,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -423,6 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -789,7 +808,7 @@
         <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.35">
@@ -1121,7 +1140,7 @@
         <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1135,7 +1154,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1149,7 +1168,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1168,7 +1187,7 @@
         <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1176,7 +1195,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1186,47 +1205,53 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CFCB2E5-50C4-494B-B397-F4A184BDF7BD}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="23.81640625" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
         <v>87</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
       </c>
       <c r="C2">
         <v>1000</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1293,7 @@
         <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H1" t="s">
         <v>31</v>
@@ -1422,7 +1447,7 @@
         <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I1" t="s">
         <v>77</v>
@@ -1751,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986D1BE3-7A15-4223-93AE-9AB753B07534}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.81640625" customWidth="1"/>
@@ -1808,11 +1833,39 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/example/GRAFS_project_example_N.xlsx
+++ b/example/GRAFS_project_example_N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938FBD28-A109-40DC-B05B-B9058FE0C8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3624EA3D-1A84-4D42-9CF9-E6652C3A5C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
   </bookViews>
   <sheets>
     <sheet name="crops" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
   <si>
     <t>Culture</t>
   </si>
@@ -303,15 +303,6 @@
     <t>Facility</t>
   </si>
   <si>
-    <t>Methanizer</t>
-  </si>
-  <si>
-    <t>Methanizer_diet</t>
-  </si>
-  <si>
-    <t>Energy Production (GWh)</t>
-  </si>
-  <si>
     <t>Weight energy production</t>
   </si>
   <si>
@@ -321,12 +312,6 @@
     <t>Energy Production (MWh/tFW)</t>
   </si>
   <si>
-    <t>Bio_diet</t>
-  </si>
-  <si>
-    <t>Bioraffinery</t>
-  </si>
-  <si>
     <t>Seed input (ktN/ktN)</t>
   </si>
   <si>
@@ -334,6 +319,9 @@
   </si>
   <si>
     <t>Total Synthetic Fertilizer Use on grasslands (ktN)</t>
+  </si>
+  <si>
+    <t>Target Energy Production (GWh)</t>
   </si>
 </sst>
 </file>
@@ -808,7 +796,7 @@
         <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.35">
@@ -1085,7 +1073,7 @@
         <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1205,11 +1193,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CFCB2E5-50C4-494B-B397-F4A184BDF7BD}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="3" max="3" width="28.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -1220,38 +1208,10 @@
         <v>81</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1253,7 @@
         <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
         <v>31</v>
@@ -1447,7 +1407,7 @@
         <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
         <v>77</v>
@@ -1841,7 +1801,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1849,7 +1809,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1857,13 +1817,13 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B10" s="8"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B11" s="8"/>
     </row>

--- a/example/GRAFS_project_example_N.xlsx
+++ b/example/GRAFS_project_example_N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E770D463-6F9C-4228-80EE-26B8ABFDC7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3976C371-5BA1-4522-9FAF-67612796AAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{092E5AC7-17CB-4282-9989-CDCB089F75B9}"/>
   </bookViews>
   <sheets>
     <sheet name="crops" sheetId="1" r:id="rId1"/>
@@ -1276,26 +1276,26 @@
     <col min="7" max="7" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1405,29 +1405,29 @@
     <col min="8" max="8" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>76</v>
       </c>
     </row>
